--- a/05_Figures/F06_prediction/proteins/acute/d_fcsa_II/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/acute/d_fcsa_II/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="184">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -140,15 +140,15 @@
     <t xml:space="preserve">FSCN1</t>
   </si>
   <si>
+    <t xml:space="preserve">GATD3B</t>
+  </si>
+  <si>
     <t xml:space="preserve">PSME3</t>
   </si>
   <si>
     <t xml:space="preserve">ACSS2</t>
   </si>
   <si>
-    <t xml:space="preserve">GATD3B</t>
-  </si>
-  <si>
     <t xml:space="preserve">BPNT1</t>
   </si>
   <si>
@@ -158,43 +158,58 @@
     <t xml:space="preserve">SEPTIN9</t>
   </si>
   <si>
+    <t xml:space="preserve">CCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USP15</t>
+  </si>
+  <si>
     <t xml:space="preserve">ARPP19</t>
   </si>
   <si>
-    <t xml:space="preserve">CCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARVA</t>
+    <t xml:space="preserve">CRIP2</t>
   </si>
   <si>
     <t xml:space="preserve">RWDD1</t>
   </si>
   <si>
+    <t xml:space="preserve">DDI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LDHB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARHGAP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP1R2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEPTIN2</t>
+  </si>
+  <si>
     <t xml:space="preserve">TKFC</t>
   </si>
   <si>
-    <t xml:space="preserve">CRIP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPB41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LDHB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARHGAP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEPTIN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USP15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDI2</t>
+    <t xml:space="preserve">CAV1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPZ1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTSG</t>
   </si>
   <si>
     <t xml:space="preserve">DLST</t>
@@ -203,376 +218,340 @@
     <t xml:space="preserve">DUSP28</t>
   </si>
   <si>
-    <t xml:space="preserve">EHD4</t>
+    <t xml:space="preserve">ECHDC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAM114A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H1-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JPT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTIF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAFAH1B3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEA15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PURA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QDPR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB11B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD23B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEC24C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSFM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VARS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AK3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKAP12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR1A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH1B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARF4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARMT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASPN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5PF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP6V1G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BROX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C11orf68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBR4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDC37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CES2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIC5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX6B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPT1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRYAB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYB5R1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHRS7B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNAJA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNLL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF1A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FBLN5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FECH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPD1L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPD2</t>
   </si>
   <si>
     <t xml:space="preserve">GSTP1</t>
   </si>
   <si>
-    <t xml:space="preserve">HNRNPA1</t>
+    <t xml:space="preserve">HADHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPA0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPA2B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITGB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LANCL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMS3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LYRM7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP1LC3B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MBNL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCCC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYPN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEDD8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NONO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PADI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCYOX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDIA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFDN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIP4K2B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRDX5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB2B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB8A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL13A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUVBL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERPINB6</t>
   </si>
   <si>
     <t xml:space="preserve">SNX5</t>
   </si>
   <si>
+    <t xml:space="preserve">SOD1</t>
+  </si>
+  <si>
     <t xml:space="preserve">STAT5B</t>
   </si>
   <si>
-    <t xml:space="preserve">TPP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSFM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAV1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPZ1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECHDC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAM114A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCLM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H1-5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ITGB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTIF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAFAH1B3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PEA15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP1R2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMB5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QDPR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB11B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD23B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC24C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VARS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AK3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKAP12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR1A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH1B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARF4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARHGAP19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASPN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5PF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP6V1G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BROX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C11orf68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CBR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDC37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CES2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIC5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX6B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPT1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRYAB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYB5R1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHRS7B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNAJA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNLL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYSF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EEF1A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FBLN5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FECH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FGGY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FTL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPD1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GPD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HADHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPA0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPA2B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JPT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LANCL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LYRM7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP1LC3B2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MBNL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCCC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPS27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYPN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAGK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NEDD8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NGLY1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NONO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PADI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCYOX1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDIA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFDN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIP4K2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPM1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP2CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRDX5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTMS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PURA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RBBP4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL13A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUVBL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERPINB6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STIM1</t>
-  </si>
-  <si>
     <t xml:space="preserve">TIGAR</t>
   </si>
   <si>
     <t xml:space="preserve">TPPP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPRKB</t>
   </si>
   <si>
     <t xml:space="preserve">TUBA1B</t>
@@ -974,16 +953,16 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.604902337890104</v>
+        <v>-0.531546275120951</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.203571428571429</v>
+        <v>-0.128571428571429</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -1007,29 +986,21 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.604902337890104</v>
+        <v>-0.531546275120951</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.203571428571429</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.592039800995025</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.606965174129353</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.582379749361231</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.569326438079574</v>
-      </c>
+        <v>-0.128571428571429</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1053,2206 +1024,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.619660879576996</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.554843604538711</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.528825946045588</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-1.40621803468655</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.394949001637251</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.536957832604612</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.109639638295729</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.148121336901082</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.304551495170289</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.7456866538699</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-1.21233966324881</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.538421609374682</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.295306981165463</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.112417860059502</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.349904061214788</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-2.29936417744384</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.582469182590767</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.475039682153949</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.132847772616855</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-1.46005987169182</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-0.8844948990017</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.411727018282176</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.613498690622808</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.368689282799515</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-1.37455179009305</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.551503249007471</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-1.37886487434419</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.406468661190891</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-1.87795241464955</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.262406712098656</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-1.01826976634152</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.0328838713938334</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.897682553922952</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0.07484342882986</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.308913301171291</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.313974812616668</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.104713078414135</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.947247097035343</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-2.35172226575209</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.0164850301946466</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-0.291548041940822</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-1.31166163275445</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0.124581861222734</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0.0336702585157722</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-1.92346102260227</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.350781900525443</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.59811525274839</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.473091691244271</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-1.12330317557821</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.209793661911656</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>0.265664081080829</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.14635197722779</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.890362045499186</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-1.1103868560376</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-0.584005927316421</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-1.55984529590584</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-1.26975942468327</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.0619443444205646</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-0.765075790294938</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.748322791790852</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-0.745508780181704</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-0.536030291576186</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-1.06889858914558</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>0.43895139664179</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-0.229547927634527</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-1.12990285442537</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0.327097609047291</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-0.142342754956193</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-0.456812747106718</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.0915632462680427</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.261481158061812</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.631085681223307</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-0.037022870898139</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-0.652453757654192</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-1.12289878331625</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-0.556252996837673</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-1.14887831154217</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.983936765810079</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-1.49094276725353</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-0.153940752565445</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.129574498107274</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-0.522902049782411</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-0.581809049072758</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.608652511135394</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.351325061564561</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-0.694619045743665</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.166031275742376</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.232071511306013</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-1.29481275109901</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-0.957518206165795</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.288436848798676</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-1.57576704933118</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-0.56727400033979</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-0.196652456483779</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-1.09219345904753</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-1.15888009941206</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.308741592439373</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-0.309324062743756</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.285159945447988</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.276683329425839</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-0.948821343331179</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>0.0874808600456914</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.207002188552205</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.544376914592421</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-0.749865850335664</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-0.397155895334252</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-1.17958428061241</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.806025396768256</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.199721059351498</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-1.31854686356013</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-1.68250251751184</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.59909787602856</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-1.04272043739517</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.489514471034603</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-0.580399961036325</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-1.52905572244085</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.260197843165394</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-0.28038461861302</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-0.591990429565505</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.965443851380124</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>0.000359449068617623</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-0.362341770289556</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-0.566356541351085</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.173825878267148</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-0.380540583869081</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-0.687262453978064</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.400141462590103</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>0.045571757961082</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-1.53828446288168</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-0.770131609071771</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-1.07464603555843</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.0924177537754398</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.36597624087426</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.0625936712524862</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.796580447776369</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.660978653270636</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-0.228597530157705</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-1.97394078851083</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.768393926774333</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-1.03387847126133</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-1.49369225094199</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.46500387423797</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-1.58241420287544</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.270680515813119</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>0.0794270630181866</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-1.33757521140303</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-0.718709849225042</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.621046553038307</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.857422472081256</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.178902591727077</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.6771973927833</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.621545509866147</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-0.365755960812788</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-1.19643872876924</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-1.20458013863823</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.299763784228676</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.237276083829808</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.691698356102457</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>0.201268022511232</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-2.00780751400789</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>0.279543993213493</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.237469502227684</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.625080445066243</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-1.6949341035139</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-1.07650649641107</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-1.26542731028555</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.185732435004492</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.0732843916947041</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-0.796163895398566</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.773668351255837</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-1.32680454676569</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-0.213511680666131</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-0.396586322265127</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.367030455567046</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>0.6660997839207</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.692326372615182</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>0.460679836269479</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.415665262247215</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>0.0460785953509644</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.464400321238987</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.330427109350229</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-0.500822263693492</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-0.0673872977404051</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>0.187811891108129</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-0.397935249086963</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.201423815590976</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>0.227373417837507</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>0.190209278437857</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-0.388196398421194</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>0.101987822479032</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.0797861672229465</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.632803559877384</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-0.272580911848841</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>0.0151832277218654</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-1.99222679126758</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-1.89380162850702</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.64651743105075</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-0.161950242628885</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-0.500746390482496</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>0.238017944716195</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3295,7 +1066,7 @@
         <v>517.34</v>
       </c>
       <c r="E2" t="n">
-        <v>1693.06299041509</v>
+        <v>1632.53648030428</v>
       </c>
     </row>
     <row r="3">
@@ -3312,7 +1083,7 @@
         <v>1517.85</v>
       </c>
       <c r="E3" t="n">
-        <v>-904.25478212839</v>
+        <v>-850.224567894635</v>
       </c>
     </row>
     <row r="4">
@@ -3329,7 +1100,7 @@
         <v>2790.83</v>
       </c>
       <c r="E4" t="n">
-        <v>-554.082419026132</v>
+        <v>-578.342734975084</v>
       </c>
     </row>
     <row r="5">
@@ -3346,7 +1117,7 @@
         <v>739.459999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>467.883198390888</v>
+        <v>392.334535899941</v>
       </c>
     </row>
     <row r="6">
@@ -3363,7 +1134,7 @@
         <v>1179</v>
       </c>
       <c r="E6" t="n">
-        <v>1676.74328078067</v>
+        <v>1716.3033463867</v>
       </c>
     </row>
     <row r="7">
@@ -3380,7 +1151,7 @@
         <v>682.55</v>
       </c>
       <c r="E7" t="n">
-        <v>2274.04414608779</v>
+        <v>2349.72717690821</v>
       </c>
     </row>
     <row r="8">
@@ -3397,7 +1168,7 @@
         <v>35.9499999999998</v>
       </c>
       <c r="E8" t="n">
-        <v>-431.70743330488</v>
+        <v>-238.417535845421</v>
       </c>
     </row>
     <row r="9">
@@ -3414,7 +1185,7 @@
         <v>-171.76</v>
       </c>
       <c r="E9" t="n">
-        <v>598.790649892932</v>
+        <v>452.736555815596</v>
       </c>
     </row>
     <row r="10">
@@ -3431,7 +1202,7 @@
         <v>854.04</v>
       </c>
       <c r="E10" t="n">
-        <v>-186.582641489426</v>
+        <v>-150.260465194878</v>
       </c>
     </row>
     <row r="11">
@@ -3448,7 +1219,7 @@
         <v>-1503.6</v>
       </c>
       <c r="E11" t="n">
-        <v>223.972115517704</v>
+        <v>157.733660098795</v>
       </c>
     </row>
     <row r="12">
@@ -3465,7 +1236,7 @@
         <v>-88.7199999999993</v>
       </c>
       <c r="E12" t="n">
-        <v>-346.369569922538</v>
+        <v>-276.998096152816</v>
       </c>
     </row>
     <row r="13">
@@ -3482,7 +1253,7 @@
         <v>-2305.05</v>
       </c>
       <c r="E13" t="n">
-        <v>396.524199413664</v>
+        <v>300.906733854128</v>
       </c>
     </row>
     <row r="14">
@@ -3499,7 +1270,7 @@
         <v>-1179.58</v>
       </c>
       <c r="E14" t="n">
-        <v>56.300913048047</v>
+        <v>-278.867798970176</v>
       </c>
     </row>
     <row r="15">
@@ -3516,7 +1287,7 @@
         <v>-1491.94</v>
       </c>
       <c r="E15" t="n">
-        <v>585.715001430915</v>
+        <v>576.568016697005</v>
       </c>
     </row>
     <row r="16">
@@ -3533,7 +1304,7 @@
         <v>-1081</v>
       </c>
       <c r="E16" t="n">
-        <v>383.806445007387</v>
+        <v>363.395381613548</v>
       </c>
     </row>
   </sheetData>
@@ -3626,10 +1397,10 @@
         <v>41</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>0.733333333333333</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
@@ -3643,10 +1414,10 @@
         <v>42</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
@@ -3677,10 +1448,10 @@
         <v>44</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.466666666666667</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9">
@@ -3694,10 +1465,10 @@
         <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.466666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -3711,10 +1482,10 @@
         <v>46</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.466666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="11">
@@ -3779,10 +1550,10 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -3796,10 +1567,10 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="16">
@@ -3830,10 +1601,10 @@
         <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>0.333333333333333</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="18">
@@ -3847,10 +1618,10 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>0.333333333333333</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="19">
@@ -3881,10 +1652,10 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>0.266666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="21">
@@ -3898,10 +1669,10 @@
         <v>57</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>0.266666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="22">
@@ -3915,10 +1686,10 @@
         <v>58</v>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>0.266666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="23">
@@ -3983,10 +1754,10 @@
         <v>62</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -4000,10 +1771,10 @@
         <v>63</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="28">
@@ -4017,10 +1788,10 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -4034,10 +1805,10 @@
         <v>65</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="30">
@@ -4051,10 +1822,10 @@
         <v>66</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="31">
@@ -4068,10 +1839,10 @@
         <v>67</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="32">
@@ -4085,10 +1856,10 @@
         <v>68</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="33">
@@ -4357,10 +2128,10 @@
         <v>84</v>
       </c>
       <c r="D48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="49">
@@ -4374,10 +2145,10 @@
         <v>85</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="50">
@@ -4391,10 +2162,10 @@
         <v>86</v>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="51">
@@ -4408,10 +2179,10 @@
         <v>87</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="52">
@@ -4425,10 +2196,10 @@
         <v>88</v>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="53">
@@ -4442,10 +2213,10 @@
         <v>89</v>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="54">
@@ -6043,125 +3814,6 @@
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="s">
-        <v>184</v>
-      </c>
-      <c r="D148" t="n">
-        <v>1</v>
-      </c>
-      <c r="E148" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="s">
-        <v>185</v>
-      </c>
-      <c r="D149" t="n">
-        <v>1</v>
-      </c>
-      <c r="E149" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="s">
-        <v>186</v>
-      </c>
-      <c r="D150" t="n">
-        <v>1</v>
-      </c>
-      <c r="E150" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="s">
-        <v>187</v>
-      </c>
-      <c r="D151" t="n">
-        <v>1</v>
-      </c>
-      <c r="E151" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="s">
-        <v>188</v>
-      </c>
-      <c r="D152" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="s">
-        <v>189</v>
-      </c>
-      <c r="D153" t="n">
-        <v>1</v>
-      </c>
-      <c r="E153" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="s">
-        <v>190</v>
-      </c>
-      <c r="D154" t="n">
-        <v>1</v>
-      </c>
-      <c r="E154" t="n">
         <v>0.0666666666666667</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/acute/d_fcsa_II/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/acute/d_fcsa_II/spls/c_data/results.xlsx
@@ -989,7 +989,7 @@
         <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.531546275120951</v>
@@ -997,10 +997,18 @@
       <c r="I3" t="n">
         <v>-0.128571428571429</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.527363184079602</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.537313432835821</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.595934729473225</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.599785344188898</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1024,6 +1032,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.202829692460666</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.414315061590882</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.538124840795751</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.42437486792255</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.238606208699818</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.582677450519275</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.0934478135935433</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.278479143891785</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.250077235775596</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.801161389995007</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-1.17216374807695</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.884031252080237</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.334583953967006</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.124721921470359</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.119549887678727</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-2.87728874951408</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.525694691019951</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.559161242021545</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.224188751167929</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.52407193360107</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.735777497285697</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.444916169079079</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.768412390880173</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.385000128687829</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-1.25185766506929</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.729802990245571</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-1.47322166152416</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.48993925467895</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-2.37375718798579</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.247577498367034</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.93945541712009</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0624288359025267</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.98310008393118</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.155113410783092</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.306519662922811</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.270667712449984</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.114527307618749</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.80738226096141</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-2.33518003949854</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.0775913292432007</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.500684401899465</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-1.37518008203732</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.104720736568485</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.00703230933729526</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-1.7047284031387</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.394460115467633</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.623289488405447</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.475130596011288</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-1.30091205874188</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.386951441743279</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.320423092423298</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.198567502621374</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.709667075308106</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.920077581896817</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.481606714772555</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-1.85063754821211</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-1.1493383475997</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.115877204266024</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.716430642476312</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.606571473053799</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.85123923429094</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.657067072523966</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-1.14159811932584</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.45173403224061</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.0622210052514486</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.827420063103265</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.156296651891699</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.0853764050476498</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.37110701021624</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.0755351399698196</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.180158620670186</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.619027667508497</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.00130177521840014</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-0.530779355294049</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-1.06109646534401</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0.934815599968262</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.96707498264202</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.93518089977644</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.976901184775106</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.302050422268195</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.0484087883123179</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.586436743301814</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.990379229548498</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.543497947780904</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.158499973519145</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.696188629338138</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0.0724209377707963</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.339756641683675</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-1.48723583626738</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-0.969437791089967</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.470465594298281</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-1.76134925655032</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-0.953429054078682</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-0.295767412474812</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-1.0930615033351</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-1.10511654980396</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.3141472043916</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.97335578103886</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.340978358023107</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.308526757599777</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.775286928237312</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.334442148356405</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.005464123822576</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.890734306133541</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.253890661055013</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.568795978755589</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-1.57108733915628</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.759674795594157</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.804027724491177</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-1.24725275195053</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-1.75632403479717</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.630784750715576</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.999797800138909</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.474490793841527</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.529003665326691</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-1.43912583898918</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.121052071964091</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-0.0495893215604744</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-0.560253929667043</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.949229089980064</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.141086690633076</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.422910040508028</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.517684027683148</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.184318407308756</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.351020059119706</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.759671058974962</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.575922412850417</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.0323364574777242</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-1.71863322888974</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.753434704396477</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-1.16151650263039</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.0410379051003955</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.350306388726492</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.00997270407720852</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.978620936064416</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.381929675397348</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.60356974528657</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-1.84299715155141</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.779191651573065</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.901401933183561</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-1.30363743526786</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.475760253146999</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-1.78432552200801</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.146602484449605</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0.107532443702364</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-1.30804949904436</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.641868195105713</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.559033377277217</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.4941533053569</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.157464699673955</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.466446788836802</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.584389474390197</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-0.409626917899543</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-1.67877320865203</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-1.04233029536681</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.392714729681587</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.170290076457726</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.658825719044737</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0.217002223329433</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-1.97674551161953</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.187619630014219</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.218147075482281</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.443375038291282</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-2.15243938466715</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-1.0755799862526</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.921825765676537</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.233891017996307</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.13477203819969</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-1.02580838463511</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.80192873638915</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-1.1276737524708</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.357438301150328</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-0.440796322640345</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.404364079246171</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0.570089125663113</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.611488440410302</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.148480577509883</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.424334558943703</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.137813835932794</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.411719755254414</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.0131086397237128</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.451932854006115</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0.211384990768748</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.0504283197354287</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-0.388316873543376</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.12880369804169</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0.159018560488676</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.353139258827866</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.431056968727211</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.0498017236020519</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.161656298880848</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-1.49044429786224</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.279685316424968</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.00581061710432151</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-2.11237788223732</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-1.73537061967361</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.555477501217094</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0.0558711832661981</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.543043339382231</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0.0212656714079869</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
